--- a/src/data/analyzed/map_data.xlsx
+++ b/src/data/analyzed/map_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-19</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="6">
@@ -513,180 +513,170 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-12</v>
+        <v>-36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-37</v>
+        <v>-17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-17</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>GR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-9</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-16</v>
+        <v>-17</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-17</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-14</v>
+        <v>-29</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-28</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-24</v>
+        <v>7.000000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-13</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-25</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-8</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-25</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-16</v>
+        <v>-35</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-36</v>
+        <v>-7.000000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-7.000000000000001</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-15</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
         <v>-13</v>
       </c>
     </row>
